--- a/docs/design-vi/ACSMS-SCR-022/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_ファイルダウンロード画面_v1.0.xlsx
+++ b/docs/design-vi/ACSMS-SCR-022/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_ファイルダウンロード画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1361,20 +1361,80 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>Đồng bộ với bản tiếng Nhật (bản này dừng ở 2026-05-27, trước cả bản JA v1.1 ngày 2026-07-02 vốn đã đổi nguồn dữ liệu): ①thay `t_file_upload`→`t_file_download`, `file_upload_id`→`file_download_id`, `アップロード日時`→`ダウンロード日時` trên toàn tài liệu. ②cập nhật danh sách cột ở TC-009 (bỏ「対象年月」, thêm「JA名」「ダウンロード種別」「操作」). ③bổ sung 11 ca kiểm thử (050〜060) và tạo カテゴリ9: cờ cho phép Nichino tải + tải hàng loạt ZIP + lọc theo loại tải, mở rộng DataScope của trung ương hội ra toàn bộ JA cùng tỉnh (#52132), và ngoại lệ không xét cờ với file do chính mình xuất</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6346,7 +6406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ68"/>
+  <dimension ref="A1:BQ80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7272,7 +7332,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Trên DB, thực thi `SELECT COUNT(*) FROM t_file_upload WHERE deleted_at IS NULL` và kiểm tra số dòng trả về có khớp không</t>
+            <t>Trên DB, thực thi `SELECT COUNT(*) FROM t_file_download WHERE deleted_at IS NULL` và kiểm tra số dòng trả về có khớp không</t>
           </r>
         </is>
       </c>
@@ -7366,7 +7426,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・NICHINO_ADMIN là role có thể tham chiếu toàn bộ dòng trong `t_file_upload`, kể cả file `ja_id IS NULL` (gửi tới toàn bộ JA) và file của JA khác
+            <t xml:space="preserve">・NICHINO_ADMIN là role có thể tham chiếu toàn bộ dòng trong `t_file_download`, kể cả file `ja_id IS NULL` (gửi tới toàn bộ JA) và file của JA khác
 </t>
           </r>
           <r>
@@ -7692,7 +7752,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Gọi trực tiếp API download GET `/api/v1/file-upload/{file_upload_id}/download` với file của JA ngoài quản hạt (`ja_id` ngoài scope)</t>
+            <t>Gọi trực tiếp API download GET `/api/v1/file-upload/{file_download_id}/download` với file của JA ngoài quản hạt (`ja_id` ngoài scope)</t>
           </r>
         </is>
       </c>
@@ -7897,7 +7957,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Lấy file ID của JA khác từ DevTools, truyền vào GET `/api/v1/file-upload/{file_upload_id}/preview` và gọi trực tiếp</t>
+            <t>Lấy file ID của JA khác từ DevTools, truyền vào GET `/api/v1/file-upload/{file_download_id}/preview` và gọi trực tiếp</t>
           </r>
         </is>
       </c>
@@ -8077,7 +8137,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Truyền trực tiếp file ID của JA khác vào GET `/api/v1/file-upload/{file_upload_id}/download` và gọi</t>
+            <t>Truyền trực tiếp file ID của JA khác vào GET `/api/v1/file-upload/{file_download_id}/download` và gọi</t>
           </r>
         </is>
       </c>
@@ -8879,7 +8939,7 @@
       <c r="BP21" s="10" t="n"/>
       <c r="BQ21" s="11" t="n"/>
     </row>
-    <row r="22" ht="384" customHeight="1">
+    <row r="22" ht="450" customHeight="1">
       <c r="A22" s="44" t="n">
         <v>9</v>
       </c>
@@ -8903,7 +8963,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・Đã login + đã xác thực MFA
-・Test data: `t_file_upload` tồn tại ≥ 5 file</t>
+・Test data: `t_file_download` tồn tại ≥ 5 file</t>
         </is>
       </c>
       <c r="K22" s="10" t="n"/>
@@ -8971,7 +9031,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Các column được hiển thị từ trái sang phải theo thứ tự `選択（チェックボックス） / アップロード日時 / 作成者 / ファイル名 / サイズ`
+            <t xml:space="preserve">Các column được hiển thị từ trái sang phải theo thứ tự `選択（チェックボックス） / ダウンロード日時 / 作成者 / JA名 / ダウンロード種別 / ファイル名 / サイズ / 操作` (column「対象年月」cũ đã bị bỏ, thêm mới column「JA名」và「ダウンロード種別」)
 </t>
           </r>
           <r>
@@ -8988,7 +9048,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Column アップロード日時 hiển thị giá trị định dạng `YYYY/MM/DD HH:mm:ss`
+            <t xml:space="preserve">・Column ダウンロード日時 hiển thị giá trị định dạng `YYYY/MM/DD HH:mm:ss` (`download_datetime`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Column JA名 hiển thị kết hợp `ja_code` + `ja_name` (file gửi toàn bộ JA với `ja_id IS NULL` thì để trống)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Column ダウンロード種別 hiển thị nhãn m_code `DOWNLOAD_TYPE` (1:口座振替 / 2:その他 / 3:増減連絡票 / 4:増減通知書 / 5:購読者名簿)
 </t>
           </r>
           <r>
@@ -9107,7 +9183,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・Đã login + đã xác thực MFA
-・Test data: `t_file_upload` tồn tại ≥ 100 file</t>
+・Test data: `t_file_download` tồn tại ≥ 100 file</t>
         </is>
       </c>
       <c r="K23" s="10" t="n"/>
@@ -11746,7 +11822,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 400 (`error_code: VALIDATION_ERROR`) — chỉ cho phép `upload_datetime / file_name / created_by`
+            <t xml:space="preserve">Trả về HTTP 400 (`error_code: VALIDATION_ERROR`) — chỉ cho phép `download_datetime / file_name / created_by`
 </t>
           </r>
           <r>
@@ -11899,7 +11975,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Nhập `'; DROP TABLE t_file_upload; --` vào textbox ファイル名 và nhấn button 検索
+            <t xml:space="preserve">Nhập `'; DROP TABLE t_file_download; --` vào textbox ファイル名 và nhấn button 検索
 </t>
           </r>
           <r>
@@ -11916,7 +11992,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Trên DB thực thi `SELECT COUNT(*) FROM t_file_upload`, xác nhận bảng vẫn tồn tại</t>
+            <t>Trên DB thực thi `SELECT COUNT(*) FROM t_file_download`, xác nhận bảng vẫn tồn tại</t>
           </r>
         </is>
       </c>
@@ -11976,7 +12052,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Bảng `t_file_upload` vẫn tồn tại (không bị phá hủy), không phát sinh sai lệch dữ liệu
+            <t xml:space="preserve">Bảng `t_file_download` vẫn tồn tại (không bị phá hủy), không phát sinh sai lệch dữ liệu
 </t>
           </r>
           <r>
@@ -12140,7 +12216,7 @@
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="46" t="inlineStr">
         <is>
-          <t>Hiển thị ban đầu — Sort mặc định (upload_datetime DESC)</t>
+          <t>Hiển thị ban đầu — Sort mặc định (download_datetime DESC)</t>
         </is>
       </c>
       <c r="F40" s="10" t="n"/>
@@ -12151,7 +12227,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・Đã login + đã xác thực MFA
-・Test data: `t_file_upload` tồn tại ≥ 5 record với upload_datetime khác nhau</t>
+・Test data: `t_file_download` tồn tại ≥ 5 record với download_datetime khác nhau</t>
         </is>
       </c>
       <c r="K40" s="10" t="n"/>
@@ -12193,7 +12269,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Kiểm tra thứ tự sắp xếp của column アップロード日時 trong danh sách kết quả
+            <t xml:space="preserve">Kiểm tra thứ tự sắp xếp của column ダウンロード日時 trong danh sách kết quả
 </t>
           </r>
           <r>
@@ -12253,7 +12329,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">アップロード日時 được xếp theo thứ tự mới nhất trước (DESC)
+            <t xml:space="preserve">ダウンロード日時 được xếp theo thứ tự mới nhất trước (DESC)
 </t>
           </r>
           <r>
@@ -12270,7 +12346,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Array `data` của response được trả về theo `upload_datetime` DESC, `meta.page = 1`, `meta.per_page = 20`
+            <t xml:space="preserve">Array `data` của response được trả về theo `download_datetime` DESC, `meta.page = 1`, `meta.per_page = 20`
 </t>
           </r>
           <r>
@@ -12287,7 +12363,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・Sort order mặc định là `upload_datetime DESC` (api.md §4.1)</t>
+            <t>・Sort order mặc định là `download_datetime DESC` (api.md §4.1)</t>
           </r>
         </is>
       </c>
@@ -12467,7 +12543,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Đi qua JOIN chain `t_file_upload.ja_id → m_ja.ja_id → m_ja.todofuken_code`
+            <t xml:space="preserve">・Đi qua JOIN chain `t_file_download.ja_id → m_ja.ja_id → m_ja.todofuken_code`
 </t>
           </r>
           <r>
@@ -12733,7 +12809,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・Đã login + đã xác thực MFA
-・Test data: trong `t_file_upload` không tồn tại file name chứa `'XYZNOTFOUND'`</t>
+・Test data: trong `t_file_download` không tồn tại file name chứa `'XYZNOTFOUND'`</t>
         </is>
       </c>
       <c r="K43" s="10" t="n"/>
@@ -12979,7 +13055,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Danh sách kết quả được hiển thị lại như danh sách mặc định (toàn bộ, `upload_datetime DESC`)
+            <t xml:space="preserve">・Danh sách kết quả được hiển thị lại như danh sách mặc định (toàn bộ, `download_datetime DESC`)
 </t>
           </r>
           <r>
@@ -13201,7 +13277,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Request được gửi dưới dạng `?file_name=zougen&amp;page=2&amp;per_page=20&amp;sort_by=upload_datetime&amp;sort_order=desc`, điều kiện search được giữ lại
+            <t xml:space="preserve">Request được gửi dưới dạng `?file_name=zougen&amp;page=2&amp;per_page=20&amp;sort_by=download_datetime&amp;sort_order=desc`, điều kiện search được giữ lại
 </t>
           </r>
           <r>
@@ -13415,7 +13491,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trở về trạng thái bỏ sort hoặc mặc định (`upload_datetime DESC`) (phụ thuộc policy FE, Sort order đúng)
+            <t xml:space="preserve">Trở về trạng thái bỏ sort hoặc mặc định (`download_datetime DESC`) (phụ thuộc policy FE, Sort order đúng)
 </t>
           </r>
           <r>
@@ -13432,7 +13508,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・Có 3 loại column sort được hỗ trợ: `upload_datetime / file_name / created_by` (api.md §4.1)</t>
+            <t>・Có 3 loại column sort được hỗ trợ: `download_datetime / file_name / created_by` (api.md §4.1)</t>
           </r>
         </is>
       </c>
@@ -13552,7 +13628,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Trên DB thực thi `SELECT COUNT(*) FROM t_file_upload WHERE deleted_at IS NULL`</t>
+            <t>Trên DB thực thi `SELECT COUNT(*) FROM t_file_download WHERE deleted_at IS NULL`</t>
           </r>
         </is>
       </c>
@@ -13812,7 +13888,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Nhấn button プレビュー, kiểm tra response của GET `/api/v1/file-upload/{file_upload_id}/preview`
+            <t xml:space="preserve">Nhấn button プレビュー, kiểm tra response của GET `/api/v1/file-upload/{file_download_id}/preview`
 </t>
           </r>
           <r>
@@ -14213,7 +14289,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Kiểm tra response của GET `/api/v1/file-upload/{file_upload_id}/preview`</t>
+            <t>Kiểm tra response của GET `/api/v1/file-upload/{file_download_id}/preview`</t>
           </r>
         </is>
       </c>
@@ -14652,7 +14728,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Kiểm tra response của GET `/api/v1/file-upload/{file_upload_id}/download`
+            <t xml:space="preserve">Kiểm tra response của GET `/api/v1/file-upload/{file_download_id}/download`
 </t>
           </r>
           <r>
@@ -14703,7 +14779,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Trên DB thực thi `SELECT * FROM t_log WHERE log_type = 4 AND operation = 'DOWNLOAD' AND target_id = :file_upload_id ORDER BY log_datetime DESC LIMIT 1`</t>
+            <t>Trên DB thực thi `SELECT * FROM t_log WHERE log_type = 4 AND operation = 'DOWNLOAD' AND target_id = :file_download_id ORDER BY log_datetime DESC LIMIT 1`</t>
           </r>
         </is>
       </c>
@@ -15293,7 +15369,7 @@
         <is>
           <t>・role: JA_HONTEN (ja_id = 5 của JA mình)
 ・Đã login + đã xác thực MFA
-・Test data: tồn tại file file_upload_id = 999 gắn JA khác (ja_id = 10)</t>
+・Test data: tồn tại file file_download_id = 999 gắn JA khác (ja_id = 10)</t>
         </is>
       </c>
       <c r="K57" s="10" t="n"/>
@@ -16818,7 +16894,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Ngắt kết nối DB (hoặc từ BE process từ chối truy cập bảng `t_file_upload`)
+            <t xml:space="preserve">Ngắt kết nối DB (hoặc từ BE process từ chối truy cập bảng `t_file_download`)
 </t>
           </r>
           <r>
@@ -16996,7 +17072,7 @@
       <c r="D66" s="11" t="n"/>
       <c r="E66" s="46" t="inlineStr">
         <is>
-          <t>NOT_FOUND — Chỉ định file_upload_id không tồn tại</t>
+          <t>NOT_FOUND — Chỉ định file_download_id không tồn tại</t>
         </is>
       </c>
       <c r="F66" s="10" t="n"/>
@@ -17186,7 +17262,7 @@
         <is>
           <t>・role: NICHINO_ADMIN
 ・Đã login + đã xác thực MFA
-・Test data: file ID = 500 tồn tại đến trước đó được xóa logical bằng `UPDATE t_file_upload SET deleted_at = NOW() WHERE file_upload_id = 500`</t>
+・Test data: file ID = 500 tồn tại đến trước đó được xóa logical bằng `UPDATE t_file_download SET deleted_at = NOW() WHERE file_download_id = 500`</t>
         </is>
       </c>
       <c r="K67" s="10" t="n"/>
@@ -17555,8 +17631,1087 @@
       <c r="BP68" s="10" t="n"/>
       <c r="BQ68" s="11" t="n"/>
     </row>
+    <row r="69" ht="22.5" customHeight="1">
+      <c r="A69" s="32" t="inlineStr">
+        <is>
+          <t>Mở rộng DataScope・Ngoại lệ cho phép tải (Scope / Download Gate)</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="n"/>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="10" t="n"/>
+      <c r="J69" s="10" t="n"/>
+      <c r="K69" s="10" t="n"/>
+      <c r="L69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
+      <c r="P69" s="10" t="n"/>
+      <c r="Q69" s="10" t="n"/>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
+      <c r="T69" s="10" t="n"/>
+      <c r="U69" s="10" t="n"/>
+      <c r="V69" s="10" t="n"/>
+      <c r="W69" s="10" t="n"/>
+      <c r="X69" s="10" t="n"/>
+      <c r="Y69" s="10" t="n"/>
+      <c r="Z69" s="10" t="n"/>
+      <c r="AA69" s="10" t="n"/>
+      <c r="AB69" s="10" t="n"/>
+      <c r="AC69" s="10" t="n"/>
+      <c r="AD69" s="10" t="n"/>
+      <c r="AE69" s="10" t="n"/>
+      <c r="AF69" s="10" t="n"/>
+      <c r="AG69" s="10" t="n"/>
+      <c r="AH69" s="10" t="n"/>
+      <c r="AI69" s="10" t="n"/>
+      <c r="AJ69" s="10" t="n"/>
+      <c r="AK69" s="10" t="n"/>
+      <c r="AL69" s="10" t="n"/>
+      <c r="AM69" s="10" t="n"/>
+      <c r="AN69" s="10" t="n"/>
+      <c r="AO69" s="10" t="n"/>
+      <c r="AP69" s="10" t="n"/>
+      <c r="AQ69" s="10" t="n"/>
+      <c r="AR69" s="10" t="n"/>
+      <c r="AS69" s="10" t="n"/>
+      <c r="AT69" s="10" t="n"/>
+      <c r="AU69" s="10" t="n"/>
+      <c r="AV69" s="10" t="n"/>
+      <c r="AW69" s="10" t="n"/>
+      <c r="AX69" s="10" t="n"/>
+      <c r="AY69" s="10" t="n"/>
+      <c r="AZ69" s="10" t="n"/>
+      <c r="BA69" s="10" t="n"/>
+      <c r="BB69" s="10" t="n"/>
+      <c r="BC69" s="10" t="n"/>
+      <c r="BD69" s="10" t="n"/>
+      <c r="BE69" s="10" t="n"/>
+      <c r="BF69" s="10" t="n"/>
+      <c r="BG69" s="10" t="n"/>
+      <c r="BH69" s="10" t="n"/>
+      <c r="BI69" s="10" t="n"/>
+      <c r="BJ69" s="10" t="n"/>
+      <c r="BK69" s="10" t="n"/>
+      <c r="BL69" s="10" t="n"/>
+      <c r="BM69" s="10" t="n"/>
+      <c r="BN69" s="10" t="n"/>
+      <c r="BO69" s="10" t="n"/>
+      <c r="BP69" s="10" t="n"/>
+      <c r="BQ69" s="11" t="n"/>
+    </row>
+    <row r="70" ht="160" customHeight="1">
+      <c r="A70" s="44" t="n">
+        <v>50</v>
+      </c>
+      <c r="B70" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-022-050</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="11" t="n"/>
+      <c r="E70" s="46" t="inlineStr">
+        <is>
+          <t>Role Nichino × nichino_download_allowed_flg=false thì cấm tải (403 + dòng bị disabled)</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="11" t="n"/>
+      <c r="J70" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN (role ID = 1)
+・Đã đăng nhập + đã xác thực MFA
+・Test data: trong `t_file_download` có 1 file với `nichino_download_allowed_flg = false` (không cho phép Nichino tải) (thực thể tồn tại trên S3)</t>
+        </is>
+      </c>
+      <c r="K70" s="10" t="n"/>
+      <c r="L70" s="10" t="n"/>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="10" t="n"/>
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="11" t="n"/>
+      <c r="Q70" s="46" t="inlineStr"/>
+      <c r="R70" s="10" t="n"/>
+      <c r="S70" s="10" t="n"/>
+      <c r="T70" s="10" t="n"/>
+      <c r="U70" s="10" t="n"/>
+      <c r="V70" s="10" t="n"/>
+      <c r="W70" s="11" t="n"/>
+      <c r="X70" s="46" t="inlineStr"/>
+      <c r="Y70" s="10" t="n"/>
+      <c r="Z70" s="10" t="n"/>
+      <c r="AA70" s="10" t="n"/>
+      <c r="AB70" s="10" t="n"/>
+      <c r="AC70" s="10" t="n"/>
+      <c r="AD70" s="11" t="n"/>
+      <c r="AE70" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF70" s="11" t="n"/>
+      <c r="AG70" s="45" t="inlineStr"/>
+      <c r="AH70" s="10" t="n"/>
+      <c r="AI70" s="11" t="n"/>
+      <c r="AJ70" s="45" t="inlineStr"/>
+      <c r="AK70" s="10" t="n"/>
+      <c r="AL70" s="11" t="n"/>
+      <c r="AM70" s="45" t="inlineStr"/>
+      <c r="AN70" s="10" t="n"/>
+      <c r="AO70" s="11" t="n"/>
+      <c r="AP70" s="45" t="inlineStr"/>
+      <c r="AQ70" s="10" t="n"/>
+      <c r="AR70" s="11" t="n"/>
+      <c r="AS70" s="45" t="inlineStr"/>
+      <c r="AT70" s="10" t="n"/>
+      <c r="AU70" s="11" t="n"/>
+      <c r="AV70" s="45" t="inlineStr"/>
+      <c r="AW70" s="10" t="n"/>
+      <c r="AX70" s="11" t="n"/>
+      <c r="AY70" s="45" t="inlineStr"/>
+      <c r="AZ70" s="10" t="n"/>
+      <c r="BA70" s="11" t="n"/>
+      <c r="BB70" s="45" t="inlineStr"/>
+      <c r="BC70" s="10" t="n"/>
+      <c r="BD70" s="11" t="n"/>
+      <c r="BE70" s="45" t="inlineStr"/>
+      <c r="BF70" s="10" t="n"/>
+      <c r="BG70" s="11" t="n"/>
+      <c r="BH70" s="45" t="inlineStr"/>
+      <c r="BI70" s="10" t="n"/>
+      <c r="BJ70" s="11" t="n"/>
+      <c r="BK70" s="46" t="inlineStr"/>
+      <c r="BL70" s="10" t="n"/>
+      <c r="BM70" s="10" t="n"/>
+      <c r="BN70" s="10" t="n"/>
+      <c r="BO70" s="10" t="n"/>
+      <c r="BP70" s="10" t="n"/>
+      <c r="BQ70" s="11" t="n"/>
+    </row>
+    <row r="71" ht="144" customHeight="1">
+      <c r="A71" s="44" t="n">
+        <v>51</v>
+      </c>
+      <c r="B71" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-022-051</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="n"/>
+      <c r="D71" s="11" t="n"/>
+      <c r="E71" s="46" t="inlineStr">
+        <is>
+          <t>Role Nichino × nichino_download_allowed_flg=true thì cho phép tải</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="n"/>
+      <c r="G71" s="10" t="n"/>
+      <c r="H71" s="10" t="n"/>
+      <c r="I71" s="11" t="n"/>
+      <c r="J71" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_STAFF (role ID = 2)
+・Đã đăng nhập + đã xác thực MFA
+・Test data: trong `t_file_download` có 1 file với `nichino_download_allowed_flg = true` (cho phép Nichino tải) (thực thể tồn tại trên S3)</t>
+        </is>
+      </c>
+      <c r="K71" s="10" t="n"/>
+      <c r="L71" s="10" t="n"/>
+      <c r="M71" s="10" t="n"/>
+      <c r="N71" s="10" t="n"/>
+      <c r="O71" s="10" t="n"/>
+      <c r="P71" s="11" t="n"/>
+      <c r="Q71" s="46" t="inlineStr"/>
+      <c r="R71" s="10" t="n"/>
+      <c r="S71" s="10" t="n"/>
+      <c r="T71" s="10" t="n"/>
+      <c r="U71" s="10" t="n"/>
+      <c r="V71" s="10" t="n"/>
+      <c r="W71" s="11" t="n"/>
+      <c r="X71" s="46" t="inlineStr"/>
+      <c r="Y71" s="10" t="n"/>
+      <c r="Z71" s="10" t="n"/>
+      <c r="AA71" s="10" t="n"/>
+      <c r="AB71" s="10" t="n"/>
+      <c r="AC71" s="10" t="n"/>
+      <c r="AD71" s="11" t="n"/>
+      <c r="AE71" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF71" s="11" t="n"/>
+      <c r="AG71" s="45" t="inlineStr"/>
+      <c r="AH71" s="10" t="n"/>
+      <c r="AI71" s="11" t="n"/>
+      <c r="AJ71" s="45" t="inlineStr"/>
+      <c r="AK71" s="10" t="n"/>
+      <c r="AL71" s="11" t="n"/>
+      <c r="AM71" s="45" t="inlineStr"/>
+      <c r="AN71" s="10" t="n"/>
+      <c r="AO71" s="11" t="n"/>
+      <c r="AP71" s="45" t="inlineStr"/>
+      <c r="AQ71" s="10" t="n"/>
+      <c r="AR71" s="11" t="n"/>
+      <c r="AS71" s="45" t="inlineStr"/>
+      <c r="AT71" s="10" t="n"/>
+      <c r="AU71" s="11" t="n"/>
+      <c r="AV71" s="45" t="inlineStr"/>
+      <c r="AW71" s="10" t="n"/>
+      <c r="AX71" s="11" t="n"/>
+      <c r="AY71" s="45" t="inlineStr"/>
+      <c r="AZ71" s="10" t="n"/>
+      <c r="BA71" s="11" t="n"/>
+      <c r="BB71" s="45" t="inlineStr"/>
+      <c r="BC71" s="10" t="n"/>
+      <c r="BD71" s="11" t="n"/>
+      <c r="BE71" s="45" t="inlineStr"/>
+      <c r="BF71" s="10" t="n"/>
+      <c r="BG71" s="11" t="n"/>
+      <c r="BH71" s="45" t="inlineStr"/>
+      <c r="BI71" s="10" t="n"/>
+      <c r="BJ71" s="11" t="n"/>
+      <c r="BK71" s="46" t="inlineStr"/>
+      <c r="BL71" s="10" t="n"/>
+      <c r="BM71" s="10" t="n"/>
+      <c r="BN71" s="10" t="n"/>
+      <c r="BO71" s="10" t="n"/>
+      <c r="BP71" s="10" t="n"/>
+      <c r="BQ71" s="11" t="n"/>
+    </row>
+    <row r="72" ht="128" customHeight="1">
+      <c r="A72" s="44" t="n">
+        <v>52</v>
+      </c>
+      <c r="B72" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-022-052</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="11" t="n"/>
+      <c r="E72" s="46" t="inlineStr">
+        <is>
+          <t>JA_HONTEN / JA_KANRI_SHITEN không bị ảnh hưởng bởi nichino_download_allowed_flg</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="11" t="n"/>
+      <c r="J72" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・Đã đăng nhập + đã xác thực MFA
+・Test data: 1 file gắn với JA của mình có `nichino_download_allowed_flg = false` (thực thể tồn tại trên S3, nằm trong DataScope)</t>
+        </is>
+      </c>
+      <c r="K72" s="10" t="n"/>
+      <c r="L72" s="10" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="11" t="n"/>
+      <c r="Q72" s="46" t="inlineStr"/>
+      <c r="R72" s="10" t="n"/>
+      <c r="S72" s="10" t="n"/>
+      <c r="T72" s="10" t="n"/>
+      <c r="U72" s="10" t="n"/>
+      <c r="V72" s="10" t="n"/>
+      <c r="W72" s="11" t="n"/>
+      <c r="X72" s="46" t="inlineStr"/>
+      <c r="Y72" s="10" t="n"/>
+      <c r="Z72" s="10" t="n"/>
+      <c r="AA72" s="10" t="n"/>
+      <c r="AB72" s="10" t="n"/>
+      <c r="AC72" s="10" t="n"/>
+      <c r="AD72" s="11" t="n"/>
+      <c r="AE72" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF72" s="11" t="n"/>
+      <c r="AG72" s="45" t="inlineStr"/>
+      <c r="AH72" s="10" t="n"/>
+      <c r="AI72" s="11" t="n"/>
+      <c r="AJ72" s="45" t="inlineStr"/>
+      <c r="AK72" s="10" t="n"/>
+      <c r="AL72" s="11" t="n"/>
+      <c r="AM72" s="45" t="inlineStr"/>
+      <c r="AN72" s="10" t="n"/>
+      <c r="AO72" s="11" t="n"/>
+      <c r="AP72" s="45" t="inlineStr"/>
+      <c r="AQ72" s="10" t="n"/>
+      <c r="AR72" s="11" t="n"/>
+      <c r="AS72" s="45" t="inlineStr"/>
+      <c r="AT72" s="10" t="n"/>
+      <c r="AU72" s="11" t="n"/>
+      <c r="AV72" s="45" t="inlineStr"/>
+      <c r="AW72" s="10" t="n"/>
+      <c r="AX72" s="11" t="n"/>
+      <c r="AY72" s="45" t="inlineStr"/>
+      <c r="AZ72" s="10" t="n"/>
+      <c r="BA72" s="11" t="n"/>
+      <c r="BB72" s="45" t="inlineStr"/>
+      <c r="BC72" s="10" t="n"/>
+      <c r="BD72" s="11" t="n"/>
+      <c r="BE72" s="45" t="inlineStr"/>
+      <c r="BF72" s="10" t="n"/>
+      <c r="BG72" s="11" t="n"/>
+      <c r="BH72" s="45" t="inlineStr"/>
+      <c r="BI72" s="10" t="n"/>
+      <c r="BJ72" s="11" t="n"/>
+      <c r="BK72" s="46" t="inlineStr"/>
+      <c r="BL72" s="10" t="n"/>
+      <c r="BM72" s="10" t="n"/>
+      <c r="BN72" s="10" t="n"/>
+      <c r="BO72" s="10" t="n"/>
+      <c r="BP72" s="10" t="n"/>
+      <c r="BQ72" s="11" t="n"/>
+    </row>
+    <row r="73" ht="64" customHeight="1">
+      <c r="A73" s="44" t="n">
+        <v>53</v>
+      </c>
+      <c r="B73" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-022-053</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="n"/>
+      <c r="D73" s="11" t="n"/>
+      <c r="E73" s="46" t="inlineStr">
+        <is>
+          <t>Gửi trực tiếp giá trị ngoài phạm vi cho phép của loại tải (download_type)</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
+      <c r="H73" s="10" t="n"/>
+      <c r="I73" s="11" t="n"/>
+      <c r="J73" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN
+・Đã đăng nhập + đã xác thực MFA</t>
+        </is>
+      </c>
+      <c r="K73" s="10" t="n"/>
+      <c r="L73" s="10" t="n"/>
+      <c r="M73" s="10" t="n"/>
+      <c r="N73" s="10" t="n"/>
+      <c r="O73" s="10" t="n"/>
+      <c r="P73" s="11" t="n"/>
+      <c r="Q73" s="46" t="inlineStr"/>
+      <c r="R73" s="10" t="n"/>
+      <c r="S73" s="10" t="n"/>
+      <c r="T73" s="10" t="n"/>
+      <c r="U73" s="10" t="n"/>
+      <c r="V73" s="10" t="n"/>
+      <c r="W73" s="11" t="n"/>
+      <c r="X73" s="46" t="inlineStr"/>
+      <c r="Y73" s="10" t="n"/>
+      <c r="Z73" s="10" t="n"/>
+      <c r="AA73" s="10" t="n"/>
+      <c r="AB73" s="10" t="n"/>
+      <c r="AC73" s="10" t="n"/>
+      <c r="AD73" s="11" t="n"/>
+      <c r="AE73" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF73" s="11" t="n"/>
+      <c r="AG73" s="45" t="inlineStr"/>
+      <c r="AH73" s="10" t="n"/>
+      <c r="AI73" s="11" t="n"/>
+      <c r="AJ73" s="45" t="inlineStr"/>
+      <c r="AK73" s="10" t="n"/>
+      <c r="AL73" s="11" t="n"/>
+      <c r="AM73" s="45" t="inlineStr"/>
+      <c r="AN73" s="10" t="n"/>
+      <c r="AO73" s="11" t="n"/>
+      <c r="AP73" s="45" t="inlineStr"/>
+      <c r="AQ73" s="10" t="n"/>
+      <c r="AR73" s="11" t="n"/>
+      <c r="AS73" s="45" t="inlineStr"/>
+      <c r="AT73" s="10" t="n"/>
+      <c r="AU73" s="11" t="n"/>
+      <c r="AV73" s="45" t="inlineStr"/>
+      <c r="AW73" s="10" t="n"/>
+      <c r="AX73" s="11" t="n"/>
+      <c r="AY73" s="45" t="inlineStr"/>
+      <c r="AZ73" s="10" t="n"/>
+      <c r="BA73" s="11" t="n"/>
+      <c r="BB73" s="45" t="inlineStr"/>
+      <c r="BC73" s="10" t="n"/>
+      <c r="BD73" s="11" t="n"/>
+      <c r="BE73" s="45" t="inlineStr"/>
+      <c r="BF73" s="10" t="n"/>
+      <c r="BG73" s="11" t="n"/>
+      <c r="BH73" s="45" t="inlineStr"/>
+      <c r="BI73" s="10" t="n"/>
+      <c r="BJ73" s="11" t="n"/>
+      <c r="BK73" s="46" t="inlineStr"/>
+      <c r="BL73" s="10" t="n"/>
+      <c r="BM73" s="10" t="n"/>
+      <c r="BN73" s="10" t="n"/>
+      <c r="BO73" s="10" t="n"/>
+      <c r="BP73" s="10" t="n"/>
+      <c r="BQ73" s="11" t="n"/>
+    </row>
+    <row r="74" ht="160" customHeight="1">
+      <c r="A74" s="44" t="n">
+        <v>54</v>
+      </c>
+      <c r="B74" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-022-054</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="n"/>
+      <c r="D74" s="11" t="n"/>
+      <c r="E74" s="46" t="inlineStr">
+        <is>
+          <t>Tìm kiếm lọc theo loại tải</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="n"/>
+      <c r="G74" s="10" t="n"/>
+      <c r="H74" s="10" t="n"/>
+      <c r="I74" s="11" t="n"/>
+      <c r="J74" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN
+・Đã đăng nhập + đã xác thực MFA
+・Test data: trong `t_file_download` có `download_type = 1` (trích nợ tài khoản) 2 file, `download_type = 4` (thông báo tăng giảm) 2 file, `download_type = 5` (danh sách người đọc) 1 file</t>
+        </is>
+      </c>
+      <c r="K74" s="10" t="n"/>
+      <c r="L74" s="10" t="n"/>
+      <c r="M74" s="10" t="n"/>
+      <c r="N74" s="10" t="n"/>
+      <c r="O74" s="10" t="n"/>
+      <c r="P74" s="11" t="n"/>
+      <c r="Q74" s="46" t="inlineStr"/>
+      <c r="R74" s="10" t="n"/>
+      <c r="S74" s="10" t="n"/>
+      <c r="T74" s="10" t="n"/>
+      <c r="U74" s="10" t="n"/>
+      <c r="V74" s="10" t="n"/>
+      <c r="W74" s="11" t="n"/>
+      <c r="X74" s="46" t="inlineStr"/>
+      <c r="Y74" s="10" t="n"/>
+      <c r="Z74" s="10" t="n"/>
+      <c r="AA74" s="10" t="n"/>
+      <c r="AB74" s="10" t="n"/>
+      <c r="AC74" s="10" t="n"/>
+      <c r="AD74" s="11" t="n"/>
+      <c r="AE74" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF74" s="11" t="n"/>
+      <c r="AG74" s="45" t="inlineStr"/>
+      <c r="AH74" s="10" t="n"/>
+      <c r="AI74" s="11" t="n"/>
+      <c r="AJ74" s="45" t="inlineStr"/>
+      <c r="AK74" s="10" t="n"/>
+      <c r="AL74" s="11" t="n"/>
+      <c r="AM74" s="45" t="inlineStr"/>
+      <c r="AN74" s="10" t="n"/>
+      <c r="AO74" s="11" t="n"/>
+      <c r="AP74" s="45" t="inlineStr"/>
+      <c r="AQ74" s="10" t="n"/>
+      <c r="AR74" s="11" t="n"/>
+      <c r="AS74" s="45" t="inlineStr"/>
+      <c r="AT74" s="10" t="n"/>
+      <c r="AU74" s="11" t="n"/>
+      <c r="AV74" s="45" t="inlineStr"/>
+      <c r="AW74" s="10" t="n"/>
+      <c r="AX74" s="11" t="n"/>
+      <c r="AY74" s="45" t="inlineStr"/>
+      <c r="AZ74" s="10" t="n"/>
+      <c r="BA74" s="11" t="n"/>
+      <c r="BB74" s="45" t="inlineStr"/>
+      <c r="BC74" s="10" t="n"/>
+      <c r="BD74" s="11" t="n"/>
+      <c r="BE74" s="45" t="inlineStr"/>
+      <c r="BF74" s="10" t="n"/>
+      <c r="BG74" s="11" t="n"/>
+      <c r="BH74" s="45" t="inlineStr"/>
+      <c r="BI74" s="10" t="n"/>
+      <c r="BJ74" s="11" t="n"/>
+      <c r="BK74" s="46" t="inlineStr"/>
+      <c r="BL74" s="10" t="n"/>
+      <c r="BM74" s="10" t="n"/>
+      <c r="BN74" s="10" t="n"/>
+      <c r="BO74" s="10" t="n"/>
+      <c r="BP74" s="10" t="n"/>
+      <c r="BQ74" s="11" t="n"/>
+    </row>
+    <row r="75" ht="128" customHeight="1">
+      <c r="A75" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="B75" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-022-055</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="n"/>
+      <c r="D75" s="11" t="n"/>
+      <c r="E75" s="46" t="inlineStr">
+        <is>
+          <t>Tải hàng loạt nhiều file (ZIP) — trường hợp bình thường</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
+      <c r="H75" s="10" t="n"/>
+      <c r="I75" s="11" t="n"/>
+      <c r="J75" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN
+・Đã đăng nhập + đã xác thực MFA
+・Test data: 5 file có thể tải mà các màn hình xuất báo biểu đã đăng ký vào `t_file_download` (thực thể tồn tại trên S3)</t>
+        </is>
+      </c>
+      <c r="K75" s="10" t="n"/>
+      <c r="L75" s="10" t="n"/>
+      <c r="M75" s="10" t="n"/>
+      <c r="N75" s="10" t="n"/>
+      <c r="O75" s="10" t="n"/>
+      <c r="P75" s="11" t="n"/>
+      <c r="Q75" s="46" t="inlineStr"/>
+      <c r="R75" s="10" t="n"/>
+      <c r="S75" s="10" t="n"/>
+      <c r="T75" s="10" t="n"/>
+      <c r="U75" s="10" t="n"/>
+      <c r="V75" s="10" t="n"/>
+      <c r="W75" s="11" t="n"/>
+      <c r="X75" s="46" t="inlineStr"/>
+      <c r="Y75" s="10" t="n"/>
+      <c r="Z75" s="10" t="n"/>
+      <c r="AA75" s="10" t="n"/>
+      <c r="AB75" s="10" t="n"/>
+      <c r="AC75" s="10" t="n"/>
+      <c r="AD75" s="11" t="n"/>
+      <c r="AE75" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF75" s="11" t="n"/>
+      <c r="AG75" s="45" t="inlineStr"/>
+      <c r="AH75" s="10" t="n"/>
+      <c r="AI75" s="11" t="n"/>
+      <c r="AJ75" s="45" t="inlineStr"/>
+      <c r="AK75" s="10" t="n"/>
+      <c r="AL75" s="11" t="n"/>
+      <c r="AM75" s="45" t="inlineStr"/>
+      <c r="AN75" s="10" t="n"/>
+      <c r="AO75" s="11" t="n"/>
+      <c r="AP75" s="45" t="inlineStr"/>
+      <c r="AQ75" s="10" t="n"/>
+      <c r="AR75" s="11" t="n"/>
+      <c r="AS75" s="45" t="inlineStr"/>
+      <c r="AT75" s="10" t="n"/>
+      <c r="AU75" s="11" t="n"/>
+      <c r="AV75" s="45" t="inlineStr"/>
+      <c r="AW75" s="10" t="n"/>
+      <c r="AX75" s="11" t="n"/>
+      <c r="AY75" s="45" t="inlineStr"/>
+      <c r="AZ75" s="10" t="n"/>
+      <c r="BA75" s="11" t="n"/>
+      <c r="BB75" s="45" t="inlineStr"/>
+      <c r="BC75" s="10" t="n"/>
+      <c r="BD75" s="11" t="n"/>
+      <c r="BE75" s="45" t="inlineStr"/>
+      <c r="BF75" s="10" t="n"/>
+      <c r="BG75" s="11" t="n"/>
+      <c r="BH75" s="45" t="inlineStr"/>
+      <c r="BI75" s="10" t="n"/>
+      <c r="BJ75" s="11" t="n"/>
+      <c r="BK75" s="46" t="inlineStr"/>
+      <c r="BL75" s="10" t="n"/>
+      <c r="BM75" s="10" t="n"/>
+      <c r="BN75" s="10" t="n"/>
+      <c r="BO75" s="10" t="n"/>
+      <c r="BP75" s="10" t="n"/>
+      <c r="BQ75" s="11" t="n"/>
+    </row>
+    <row r="76" ht="48" customHeight="1">
+      <c r="A76" s="44" t="n">
+        <v>56</v>
+      </c>
+      <c r="B76" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-022-056</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="11" t="n"/>
+      <c r="E76" s="46" t="inlineStr">
+        <is>
+          <t>Tải hàng loạt ZIP — chọn 0 file (chưa chọn file)</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="10" t="n"/>
+      <c r="I76" s="11" t="n"/>
+      <c r="J76" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN
+・Đã đăng nhập + đã xác thực MFA</t>
+        </is>
+      </c>
+      <c r="K76" s="10" t="n"/>
+      <c r="L76" s="10" t="n"/>
+      <c r="M76" s="10" t="n"/>
+      <c r="N76" s="10" t="n"/>
+      <c r="O76" s="10" t="n"/>
+      <c r="P76" s="11" t="n"/>
+      <c r="Q76" s="46" t="inlineStr"/>
+      <c r="R76" s="10" t="n"/>
+      <c r="S76" s="10" t="n"/>
+      <c r="T76" s="10" t="n"/>
+      <c r="U76" s="10" t="n"/>
+      <c r="V76" s="10" t="n"/>
+      <c r="W76" s="11" t="n"/>
+      <c r="X76" s="46" t="inlineStr"/>
+      <c r="Y76" s="10" t="n"/>
+      <c r="Z76" s="10" t="n"/>
+      <c r="AA76" s="10" t="n"/>
+      <c r="AB76" s="10" t="n"/>
+      <c r="AC76" s="10" t="n"/>
+      <c r="AD76" s="11" t="n"/>
+      <c r="AE76" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF76" s="11" t="n"/>
+      <c r="AG76" s="45" t="inlineStr"/>
+      <c r="AH76" s="10" t="n"/>
+      <c r="AI76" s="11" t="n"/>
+      <c r="AJ76" s="45" t="inlineStr"/>
+      <c r="AK76" s="10" t="n"/>
+      <c r="AL76" s="11" t="n"/>
+      <c r="AM76" s="45" t="inlineStr"/>
+      <c r="AN76" s="10" t="n"/>
+      <c r="AO76" s="11" t="n"/>
+      <c r="AP76" s="45" t="inlineStr"/>
+      <c r="AQ76" s="10" t="n"/>
+      <c r="AR76" s="11" t="n"/>
+      <c r="AS76" s="45" t="inlineStr"/>
+      <c r="AT76" s="10" t="n"/>
+      <c r="AU76" s="11" t="n"/>
+      <c r="AV76" s="45" t="inlineStr"/>
+      <c r="AW76" s="10" t="n"/>
+      <c r="AX76" s="11" t="n"/>
+      <c r="AY76" s="45" t="inlineStr"/>
+      <c r="AZ76" s="10" t="n"/>
+      <c r="BA76" s="11" t="n"/>
+      <c r="BB76" s="45" t="inlineStr"/>
+      <c r="BC76" s="10" t="n"/>
+      <c r="BD76" s="11" t="n"/>
+      <c r="BE76" s="45" t="inlineStr"/>
+      <c r="BF76" s="10" t="n"/>
+      <c r="BG76" s="11" t="n"/>
+      <c r="BH76" s="45" t="inlineStr"/>
+      <c r="BI76" s="10" t="n"/>
+      <c r="BJ76" s="11" t="n"/>
+      <c r="BK76" s="46" t="inlineStr"/>
+      <c r="BL76" s="10" t="n"/>
+      <c r="BM76" s="10" t="n"/>
+      <c r="BN76" s="10" t="n"/>
+      <c r="BO76" s="10" t="n"/>
+      <c r="BP76" s="10" t="n"/>
+      <c r="BQ76" s="11" t="n"/>
+    </row>
+    <row r="77" ht="80" customHeight="1">
+      <c r="A77" s="44" t="n">
+        <v>57</v>
+      </c>
+      <c r="B77" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-022-057</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="n"/>
+      <c r="D77" s="11" t="n"/>
+      <c r="E77" s="46" t="inlineStr">
+        <is>
+          <t>Tải hàng loạt ZIP — chọn 51 file (vượt giới hạn)</t>
+        </is>
+      </c>
+      <c r="F77" s="10" t="n"/>
+      <c r="G77" s="10" t="n"/>
+      <c r="H77" s="10" t="n"/>
+      <c r="I77" s="11" t="n"/>
+      <c r="J77" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN
+・Đã đăng nhập + đã xác thực MFA
+・Test data: tồn tại từ 51 file có thể tải trở lên</t>
+        </is>
+      </c>
+      <c r="K77" s="10" t="n"/>
+      <c r="L77" s="10" t="n"/>
+      <c r="M77" s="10" t="n"/>
+      <c r="N77" s="10" t="n"/>
+      <c r="O77" s="10" t="n"/>
+      <c r="P77" s="11" t="n"/>
+      <c r="Q77" s="46" t="inlineStr"/>
+      <c r="R77" s="10" t="n"/>
+      <c r="S77" s="10" t="n"/>
+      <c r="T77" s="10" t="n"/>
+      <c r="U77" s="10" t="n"/>
+      <c r="V77" s="10" t="n"/>
+      <c r="W77" s="11" t="n"/>
+      <c r="X77" s="46" t="inlineStr"/>
+      <c r="Y77" s="10" t="n"/>
+      <c r="Z77" s="10" t="n"/>
+      <c r="AA77" s="10" t="n"/>
+      <c r="AB77" s="10" t="n"/>
+      <c r="AC77" s="10" t="n"/>
+      <c r="AD77" s="11" t="n"/>
+      <c r="AE77" s="45" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF77" s="11" t="n"/>
+      <c r="AG77" s="45" t="inlineStr"/>
+      <c r="AH77" s="10" t="n"/>
+      <c r="AI77" s="11" t="n"/>
+      <c r="AJ77" s="45" t="inlineStr"/>
+      <c r="AK77" s="10" t="n"/>
+      <c r="AL77" s="11" t="n"/>
+      <c r="AM77" s="45" t="inlineStr"/>
+      <c r="AN77" s="10" t="n"/>
+      <c r="AO77" s="11" t="n"/>
+      <c r="AP77" s="45" t="inlineStr"/>
+      <c r="AQ77" s="10" t="n"/>
+      <c r="AR77" s="11" t="n"/>
+      <c r="AS77" s="45" t="inlineStr"/>
+      <c r="AT77" s="10" t="n"/>
+      <c r="AU77" s="11" t="n"/>
+      <c r="AV77" s="45" t="inlineStr"/>
+      <c r="AW77" s="10" t="n"/>
+      <c r="AX77" s="11" t="n"/>
+      <c r="AY77" s="45" t="inlineStr"/>
+      <c r="AZ77" s="10" t="n"/>
+      <c r="BA77" s="11" t="n"/>
+      <c r="BB77" s="45" t="inlineStr"/>
+      <c r="BC77" s="10" t="n"/>
+      <c r="BD77" s="11" t="n"/>
+      <c r="BE77" s="45" t="inlineStr"/>
+      <c r="BF77" s="10" t="n"/>
+      <c r="BG77" s="11" t="n"/>
+      <c r="BH77" s="45" t="inlineStr"/>
+      <c r="BI77" s="10" t="n"/>
+      <c r="BJ77" s="11" t="n"/>
+      <c r="BK77" s="46" t="inlineStr"/>
+      <c r="BL77" s="10" t="n"/>
+      <c r="BM77" s="10" t="n"/>
+      <c r="BN77" s="10" t="n"/>
+      <c r="BO77" s="10" t="n"/>
+      <c r="BP77" s="10" t="n"/>
+      <c r="BQ77" s="11" t="n"/>
+    </row>
+    <row r="78" ht="80" customHeight="1">
+      <c r="A78" s="44" t="n">
+        <v>58</v>
+      </c>
+      <c r="B78" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-022-058</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="11" t="n"/>
+      <c r="E78" s="46" t="inlineStr">
+        <is>
+          <t>Tải hàng loạt ZIP — chỉ định ID trùng lặp</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="11" t="n"/>
+      <c r="J78" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN
+・Đã đăng nhập + đã xác thực MFA
+・Test data: tồn tại từ 2 file có thể tải trở lên</t>
+        </is>
+      </c>
+      <c r="K78" s="10" t="n"/>
+      <c r="L78" s="10" t="n"/>
+      <c r="M78" s="10" t="n"/>
+      <c r="N78" s="10" t="n"/>
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="11" t="n"/>
+      <c r="Q78" s="46" t="inlineStr"/>
+      <c r="R78" s="10" t="n"/>
+      <c r="S78" s="10" t="n"/>
+      <c r="T78" s="10" t="n"/>
+      <c r="U78" s="10" t="n"/>
+      <c r="V78" s="10" t="n"/>
+      <c r="W78" s="11" t="n"/>
+      <c r="X78" s="46" t="inlineStr"/>
+      <c r="Y78" s="10" t="n"/>
+      <c r="Z78" s="10" t="n"/>
+      <c r="AA78" s="10" t="n"/>
+      <c r="AB78" s="10" t="n"/>
+      <c r="AC78" s="10" t="n"/>
+      <c r="AD78" s="11" t="n"/>
+      <c r="AE78" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF78" s="11" t="n"/>
+      <c r="AG78" s="45" t="inlineStr"/>
+      <c r="AH78" s="10" t="n"/>
+      <c r="AI78" s="11" t="n"/>
+      <c r="AJ78" s="45" t="inlineStr"/>
+      <c r="AK78" s="10" t="n"/>
+      <c r="AL78" s="11" t="n"/>
+      <c r="AM78" s="45" t="inlineStr"/>
+      <c r="AN78" s="10" t="n"/>
+      <c r="AO78" s="11" t="n"/>
+      <c r="AP78" s="45" t="inlineStr"/>
+      <c r="AQ78" s="10" t="n"/>
+      <c r="AR78" s="11" t="n"/>
+      <c r="AS78" s="45" t="inlineStr"/>
+      <c r="AT78" s="10" t="n"/>
+      <c r="AU78" s="11" t="n"/>
+      <c r="AV78" s="45" t="inlineStr"/>
+      <c r="AW78" s="10" t="n"/>
+      <c r="AX78" s="11" t="n"/>
+      <c r="AY78" s="45" t="inlineStr"/>
+      <c r="AZ78" s="10" t="n"/>
+      <c r="BA78" s="11" t="n"/>
+      <c r="BB78" s="45" t="inlineStr"/>
+      <c r="BC78" s="10" t="n"/>
+      <c r="BD78" s="11" t="n"/>
+      <c r="BE78" s="45" t="inlineStr"/>
+      <c r="BF78" s="10" t="n"/>
+      <c r="BG78" s="11" t="n"/>
+      <c r="BH78" s="45" t="inlineStr"/>
+      <c r="BI78" s="10" t="n"/>
+      <c r="BJ78" s="11" t="n"/>
+      <c r="BK78" s="46" t="inlineStr"/>
+      <c r="BL78" s="10" t="n"/>
+      <c r="BM78" s="10" t="n"/>
+      <c r="BN78" s="10" t="n"/>
+      <c r="BO78" s="10" t="n"/>
+      <c r="BP78" s="10" t="n"/>
+      <c r="BQ78" s="11" t="n"/>
+    </row>
+    <row r="79" ht="256" customHeight="1">
+      <c r="A79" s="44" t="n">
+        <v>59</v>
+      </c>
+      <c r="B79" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-022-059</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="n"/>
+      <c r="D79" s="11" t="n"/>
+      <c r="E79" s="46" t="inlineStr">
+        <is>
+          <t>Mở rộng DataScope của trung ương hội — toàn bộ JA cùng tỉnh (#52132)</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="11" t="n"/>
+      <c r="J79" s="46" t="inlineStr">
+        <is>
+          <t>・role: CHUOKAI (JA của mình = ja_id 5, `todofuken_code='13'`)
+・Cùng tỉnh (13) có 2 JA khác ngoài JA của mình, mỗi JA đã xuất file
+・Có 1 file của JA thuộc tỉnh khác (ví dụ: 14)
+・File của JA cùng tỉnh phải chuẩn bị cả loại `nichino_download_allowed_flg = true` và `false`
+・Chuẩn bị cả session **không có** `todofuken_code` (được phát hành trước khi triển khai tính năng này)</t>
+        </is>
+      </c>
+      <c r="K79" s="10" t="n"/>
+      <c r="L79" s="10" t="n"/>
+      <c r="M79" s="10" t="n"/>
+      <c r="N79" s="10" t="n"/>
+      <c r="O79" s="10" t="n"/>
+      <c r="P79" s="11" t="n"/>
+      <c r="Q79" s="46" t="inlineStr"/>
+      <c r="R79" s="10" t="n"/>
+      <c r="S79" s="10" t="n"/>
+      <c r="T79" s="10" t="n"/>
+      <c r="U79" s="10" t="n"/>
+      <c r="V79" s="10" t="n"/>
+      <c r="W79" s="11" t="n"/>
+      <c r="X79" s="46" t="inlineStr"/>
+      <c r="Y79" s="10" t="n"/>
+      <c r="Z79" s="10" t="n"/>
+      <c r="AA79" s="10" t="n"/>
+      <c r="AB79" s="10" t="n"/>
+      <c r="AC79" s="10" t="n"/>
+      <c r="AD79" s="11" t="n"/>
+      <c r="AE79" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF79" s="11" t="n"/>
+      <c r="AG79" s="45" t="inlineStr"/>
+      <c r="AH79" s="10" t="n"/>
+      <c r="AI79" s="11" t="n"/>
+      <c r="AJ79" s="45" t="inlineStr"/>
+      <c r="AK79" s="10" t="n"/>
+      <c r="AL79" s="11" t="n"/>
+      <c r="AM79" s="45" t="inlineStr"/>
+      <c r="AN79" s="10" t="n"/>
+      <c r="AO79" s="11" t="n"/>
+      <c r="AP79" s="45" t="inlineStr"/>
+      <c r="AQ79" s="10" t="n"/>
+      <c r="AR79" s="11" t="n"/>
+      <c r="AS79" s="45" t="inlineStr"/>
+      <c r="AT79" s="10" t="n"/>
+      <c r="AU79" s="11" t="n"/>
+      <c r="AV79" s="45" t="inlineStr"/>
+      <c r="AW79" s="10" t="n"/>
+      <c r="AX79" s="11" t="n"/>
+      <c r="AY79" s="45" t="inlineStr"/>
+      <c r="AZ79" s="10" t="n"/>
+      <c r="BA79" s="11" t="n"/>
+      <c r="BB79" s="45" t="inlineStr"/>
+      <c r="BC79" s="10" t="n"/>
+      <c r="BD79" s="11" t="n"/>
+      <c r="BE79" s="45" t="inlineStr"/>
+      <c r="BF79" s="10" t="n"/>
+      <c r="BG79" s="11" t="n"/>
+      <c r="BH79" s="45" t="inlineStr"/>
+      <c r="BI79" s="10" t="n"/>
+      <c r="BJ79" s="11" t="n"/>
+      <c r="BK79" s="46" t="inlineStr"/>
+      <c r="BL79" s="10" t="n"/>
+      <c r="BM79" s="10" t="n"/>
+      <c r="BN79" s="10" t="n"/>
+      <c r="BO79" s="10" t="n"/>
+      <c r="BP79" s="10" t="n"/>
+      <c r="BQ79" s="11" t="n"/>
+    </row>
+    <row r="80" ht="288" customHeight="1">
+      <c r="A80" s="44" t="n">
+        <v>60</v>
+      </c>
+      <c r="B80" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-022-060</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="n"/>
+      <c r="D80" s="11" t="n"/>
+      <c r="E80" s="46" t="inlineStr">
+        <is>
+          <t>Cho phép tải của Nichino — Thêm trung ương hội vào đối tượng và ngoại lệ cho file do chính mình xuất (#52132)</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
+      <c r="H80" s="10" t="n"/>
+      <c r="I80" s="11" t="n"/>
+      <c r="J80" s="46" t="inlineStr">
+        <is>
+          <t>・Chuẩn bị các file sau
+・(a) `nichino_download_allowed_flg = false`・`created_by` = **tài khoản khác**
+・(b) `nichino_download_allowed_flg = false`・`created_by` = **`account_id` của tài khoản đang đăng nhập**
+・(c) `nichino_download_allowed_flg = false`・`created_by` = **chuỗi rỗng**
+・(d) `nichino_download_allowed_flg = true`・`created_by` = tài khoản khác
+・Các tài khoản role: NICHINO_ADMIN / NICHINO_STAFF / CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN</t>
+        </is>
+      </c>
+      <c r="K80" s="10" t="n"/>
+      <c r="L80" s="10" t="n"/>
+      <c r="M80" s="10" t="n"/>
+      <c r="N80" s="10" t="n"/>
+      <c r="O80" s="10" t="n"/>
+      <c r="P80" s="11" t="n"/>
+      <c r="Q80" s="46" t="inlineStr"/>
+      <c r="R80" s="10" t="n"/>
+      <c r="S80" s="10" t="n"/>
+      <c r="T80" s="10" t="n"/>
+      <c r="U80" s="10" t="n"/>
+      <c r="V80" s="10" t="n"/>
+      <c r="W80" s="11" t="n"/>
+      <c r="X80" s="46" t="inlineStr"/>
+      <c r="Y80" s="10" t="n"/>
+      <c r="Z80" s="10" t="n"/>
+      <c r="AA80" s="10" t="n"/>
+      <c r="AB80" s="10" t="n"/>
+      <c r="AC80" s="10" t="n"/>
+      <c r="AD80" s="11" t="n"/>
+      <c r="AE80" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF80" s="11" t="n"/>
+      <c r="AG80" s="45" t="inlineStr"/>
+      <c r="AH80" s="10" t="n"/>
+      <c r="AI80" s="11" t="n"/>
+      <c r="AJ80" s="45" t="inlineStr"/>
+      <c r="AK80" s="10" t="n"/>
+      <c r="AL80" s="11" t="n"/>
+      <c r="AM80" s="45" t="inlineStr"/>
+      <c r="AN80" s="10" t="n"/>
+      <c r="AO80" s="11" t="n"/>
+      <c r="AP80" s="45" t="inlineStr"/>
+      <c r="AQ80" s="10" t="n"/>
+      <c r="AR80" s="11" t="n"/>
+      <c r="AS80" s="45" t="inlineStr"/>
+      <c r="AT80" s="10" t="n"/>
+      <c r="AU80" s="11" t="n"/>
+      <c r="AV80" s="45" t="inlineStr"/>
+      <c r="AW80" s="10" t="n"/>
+      <c r="AX80" s="11" t="n"/>
+      <c r="AY80" s="45" t="inlineStr"/>
+      <c r="AZ80" s="10" t="n"/>
+      <c r="BA80" s="11" t="n"/>
+      <c r="BB80" s="45" t="inlineStr"/>
+      <c r="BC80" s="10" t="n"/>
+      <c r="BD80" s="11" t="n"/>
+      <c r="BE80" s="45" t="inlineStr"/>
+      <c r="BF80" s="10" t="n"/>
+      <c r="BG80" s="11" t="n"/>
+      <c r="BH80" s="45" t="inlineStr"/>
+      <c r="BI80" s="10" t="n"/>
+      <c r="BJ80" s="11" t="n"/>
+      <c r="BK80" s="46" t="inlineStr"/>
+      <c r="BL80" s="10" t="n"/>
+      <c r="BM80" s="10" t="n"/>
+      <c r="BN80" s="10" t="n"/>
+      <c r="BO80" s="10" t="n"/>
+      <c r="BP80" s="10" t="n"/>
+      <c r="BQ80" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="907">
+  <mergeCells count="1095">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="Q27:W27"/>
@@ -17588,37 +18743,54 @@
     <mergeCell ref="AM65:AO65"/>
     <mergeCell ref="AG24:AI24"/>
     <mergeCell ref="J57:P57"/>
+    <mergeCell ref="BB77:BD77"/>
     <mergeCell ref="W2:AH2"/>
+    <mergeCell ref="B80:D80"/>
     <mergeCell ref="X10:AD11"/>
     <mergeCell ref="A26:BQ26"/>
     <mergeCell ref="AG42:AI42"/>
+    <mergeCell ref="BK70:BQ70"/>
     <mergeCell ref="AJ22:AL22"/>
+    <mergeCell ref="AY74:BA74"/>
     <mergeCell ref="AP13:AR13"/>
+    <mergeCell ref="AS74:AU74"/>
+    <mergeCell ref="AV75:AX75"/>
     <mergeCell ref="BK42:BQ42"/>
     <mergeCell ref="Q38:W38"/>
     <mergeCell ref="AE34:AF34"/>
+    <mergeCell ref="AY76:BA76"/>
     <mergeCell ref="AJ51:AL51"/>
+    <mergeCell ref="AP71:AR71"/>
     <mergeCell ref="BK47:BQ47"/>
     <mergeCell ref="E25:I25"/>
+    <mergeCell ref="X74:AD74"/>
     <mergeCell ref="X68:AD68"/>
     <mergeCell ref="Q40:W40"/>
+    <mergeCell ref="AS76:AU76"/>
     <mergeCell ref="AE36:AF36"/>
     <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="Q15:W15"/>
+    <mergeCell ref="AV70:AX70"/>
     <mergeCell ref="E58:I58"/>
+    <mergeCell ref="AP79:AR79"/>
     <mergeCell ref="BE20:BG20"/>
     <mergeCell ref="BH21:BJ21"/>
     <mergeCell ref="AM34:AO34"/>
     <mergeCell ref="AJ38:AL38"/>
+    <mergeCell ref="AP73:AR73"/>
+    <mergeCell ref="X76:AD76"/>
+    <mergeCell ref="J75:P75"/>
     <mergeCell ref="BE35:BG35"/>
     <mergeCell ref="AM49:AO49"/>
     <mergeCell ref="AE50:AF50"/>
     <mergeCell ref="AG52:AI52"/>
+    <mergeCell ref="B73:D73"/>
     <mergeCell ref="BE22:BG22"/>
     <mergeCell ref="BH23:BJ23"/>
     <mergeCell ref="AE31:AF31"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="AG45:AI45"/>
+    <mergeCell ref="AM78:AO78"/>
     <mergeCell ref="AS67:AU67"/>
     <mergeCell ref="AY29:BA29"/>
     <mergeCell ref="E20:I20"/>
@@ -17626,6 +18798,7 @@
     <mergeCell ref="AG37:AI37"/>
     <mergeCell ref="X21:AD21"/>
     <mergeCell ref="AE62:AF62"/>
+    <mergeCell ref="B74:D74"/>
     <mergeCell ref="AG47:AI47"/>
     <mergeCell ref="B68:D68"/>
     <mergeCell ref="AF8:AH8"/>
@@ -17633,15 +18806,19 @@
     <mergeCell ref="AY31:BA31"/>
     <mergeCell ref="AJ35:AL35"/>
     <mergeCell ref="BK37:BQ37"/>
+    <mergeCell ref="Q77:W77"/>
+    <mergeCell ref="E78:I78"/>
     <mergeCell ref="AM55:AO55"/>
     <mergeCell ref="BH34:BJ34"/>
     <mergeCell ref="X23:AD23"/>
     <mergeCell ref="BE38:BG38"/>
     <mergeCell ref="AE64:AF64"/>
+    <mergeCell ref="B76:D76"/>
     <mergeCell ref="AS62:AU62"/>
     <mergeCell ref="AV63:AX63"/>
     <mergeCell ref="AP66:AR66"/>
     <mergeCell ref="BH49:BJ49"/>
+    <mergeCell ref="E80:I80"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="BK66:BQ66"/>
     <mergeCell ref="X16:AD16"/>
@@ -17649,6 +18826,7 @@
     <mergeCell ref="AE57:AF57"/>
     <mergeCell ref="AS64:AU64"/>
     <mergeCell ref="AC7:AE7"/>
+    <mergeCell ref="Q72:W72"/>
     <mergeCell ref="BE15:BG15"/>
     <mergeCell ref="AP68:AR68"/>
     <mergeCell ref="J65:P65"/>
@@ -17659,6 +18837,7 @@
     <mergeCell ref="AG50:AI50"/>
     <mergeCell ref="AP67:AR67"/>
     <mergeCell ref="BK13:BQ13"/>
+    <mergeCell ref="BE79:BG79"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="AY57:BA57"/>
     <mergeCell ref="AM58:AO58"/>
@@ -17668,6 +18847,7 @@
     <mergeCell ref="Q46:W46"/>
     <mergeCell ref="BH55:BJ55"/>
     <mergeCell ref="AM24:AO24"/>
+    <mergeCell ref="AJ72:AL72"/>
     <mergeCell ref="AG27:AI27"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="BB38:BD38"/>
@@ -17675,9 +18855,12 @@
     <mergeCell ref="Q61:W61"/>
     <mergeCell ref="W3:AH3"/>
     <mergeCell ref="E33:I33"/>
+    <mergeCell ref="BK79:BQ79"/>
+    <mergeCell ref="AE75:AF75"/>
     <mergeCell ref="AV13:AX13"/>
     <mergeCell ref="BH42:BJ42"/>
     <mergeCell ref="AS17:AU17"/>
+    <mergeCell ref="AV78:AX78"/>
     <mergeCell ref="AS11:AU11"/>
     <mergeCell ref="BB40:BD40"/>
     <mergeCell ref="BH29:BJ29"/>
@@ -17686,10 +18869,13 @@
     <mergeCell ref="AY44:BA44"/>
     <mergeCell ref="BH44:BJ44"/>
     <mergeCell ref="Q56:W56"/>
+    <mergeCell ref="AS75:AU75"/>
+    <mergeCell ref="X77:AD77"/>
     <mergeCell ref="AE52:AF52"/>
     <mergeCell ref="Q43:W43"/>
     <mergeCell ref="J14:P14"/>
     <mergeCell ref="B51:D51"/>
+    <mergeCell ref="E74:I74"/>
     <mergeCell ref="AM50:AO50"/>
     <mergeCell ref="AJ54:AL54"/>
     <mergeCell ref="AM15:AO15"/>
@@ -17699,14 +18885,19 @@
     <mergeCell ref="BE34:BG34"/>
     <mergeCell ref="BE28:BG28"/>
     <mergeCell ref="AJ41:AL41"/>
+    <mergeCell ref="AM80:AO80"/>
+    <mergeCell ref="J78:P78"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="BK10:BQ11"/>
     <mergeCell ref="AS14:AU14"/>
+    <mergeCell ref="AM79:AO79"/>
     <mergeCell ref="AG55:AI55"/>
     <mergeCell ref="AP18:AR18"/>
     <mergeCell ref="AJ56:AL56"/>
     <mergeCell ref="AG38:AI38"/>
     <mergeCell ref="AJ43:AL43"/>
+    <mergeCell ref="AY70:BA70"/>
+    <mergeCell ref="J80:P80"/>
     <mergeCell ref="AV25:AX25"/>
     <mergeCell ref="W6:Y6"/>
     <mergeCell ref="J55:P55"/>
@@ -17720,7 +18911,9 @@
     <mergeCell ref="X24:AD24"/>
     <mergeCell ref="BB43:BD43"/>
     <mergeCell ref="BK68:BQ68"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="AY47:BA47"/>
+    <mergeCell ref="AS72:AU72"/>
     <mergeCell ref="E21:I21"/>
     <mergeCell ref="BH50:BJ50"/>
     <mergeCell ref="Q36:W36"/>
@@ -17734,6 +18927,8 @@
     <mergeCell ref="E23:I23"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="BE56:BG56"/>
+    <mergeCell ref="AM70:AO70"/>
+    <mergeCell ref="AE71:AF71"/>
     <mergeCell ref="BE43:BG43"/>
     <mergeCell ref="J33:P33"/>
     <mergeCell ref="AE58:AF58"/>
@@ -17743,41 +18938,52 @@
     <mergeCell ref="X27:AD27"/>
     <mergeCell ref="AG66:AI66"/>
     <mergeCell ref="BB46:BD46"/>
+    <mergeCell ref="AM74:AO74"/>
     <mergeCell ref="BE57:BG57"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="BB61:BD61"/>
+    <mergeCell ref="AG74:AI74"/>
     <mergeCell ref="AV15:AX15"/>
     <mergeCell ref="AY16:BA16"/>
     <mergeCell ref="Q62:W62"/>
     <mergeCell ref="E34:I34"/>
     <mergeCell ref="AG68:AI68"/>
     <mergeCell ref="AG43:AI43"/>
+    <mergeCell ref="AP72:AR72"/>
+    <mergeCell ref="AM76:AO76"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="E49:I49"/>
     <mergeCell ref="J68:P68"/>
+    <mergeCell ref="AV79:AX79"/>
     <mergeCell ref="AY18:BA18"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="AY45:BA45"/>
     <mergeCell ref="E36:I36"/>
     <mergeCell ref="Q64:W64"/>
     <mergeCell ref="Q51:W51"/>
+    <mergeCell ref="BH70:BJ70"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AV65:AX65"/>
     <mergeCell ref="BH45:BJ45"/>
     <mergeCell ref="AS20:AU20"/>
     <mergeCell ref="A53:BQ53"/>
+    <mergeCell ref="E76:I76"/>
     <mergeCell ref="AP24:AR24"/>
     <mergeCell ref="BH32:BJ32"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="BK18:BQ18"/>
     <mergeCell ref="A19:BQ19"/>
     <mergeCell ref="AY22:BA22"/>
+    <mergeCell ref="AE80:AF80"/>
     <mergeCell ref="BH47:BJ47"/>
     <mergeCell ref="AS22:AU22"/>
     <mergeCell ref="X20:AD20"/>
+    <mergeCell ref="BH72:BJ72"/>
     <mergeCell ref="X14:AD14"/>
     <mergeCell ref="AY42:BA42"/>
     <mergeCell ref="AE55:AF55"/>
+    <mergeCell ref="BH74:BJ74"/>
+    <mergeCell ref="AG80:AI80"/>
     <mergeCell ref="AG21:AI21"/>
     <mergeCell ref="X38:AD38"/>
     <mergeCell ref="B42:D42"/>
@@ -17787,6 +18993,7 @@
     <mergeCell ref="BE44:BG44"/>
     <mergeCell ref="AJ57:AL57"/>
     <mergeCell ref="AG61:AI61"/>
+    <mergeCell ref="BH76:BJ76"/>
     <mergeCell ref="BE31:BG31"/>
     <mergeCell ref="J21:P21"/>
     <mergeCell ref="A1:E1"/>
@@ -17799,33 +19006,44 @@
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="BH58:BJ58"/>
     <mergeCell ref="AV28:AX28"/>
+    <mergeCell ref="Q75:W75"/>
     <mergeCell ref="BK44:BQ44"/>
     <mergeCell ref="BB49:BD49"/>
     <mergeCell ref="AG62:AI62"/>
     <mergeCell ref="AE33:AF33"/>
     <mergeCell ref="BB36:BD36"/>
+    <mergeCell ref="AV74:AX74"/>
+    <mergeCell ref="AP77:AR77"/>
     <mergeCell ref="X40:AD40"/>
     <mergeCell ref="E31:I31"/>
     <mergeCell ref="AV36:AX36"/>
+    <mergeCell ref="BK77:BQ77"/>
     <mergeCell ref="T6:V6"/>
     <mergeCell ref="B20:D20"/>
+    <mergeCell ref="AE73:AF73"/>
     <mergeCell ref="Q52:W52"/>
     <mergeCell ref="AS33:AU33"/>
+    <mergeCell ref="AJ75:AL75"/>
     <mergeCell ref="AM36:AO36"/>
     <mergeCell ref="F1:Q1"/>
     <mergeCell ref="AP37:AR37"/>
     <mergeCell ref="J34:P34"/>
     <mergeCell ref="AY37:BA37"/>
     <mergeCell ref="BE65:BG65"/>
+    <mergeCell ref="BK72:BQ72"/>
     <mergeCell ref="AS35:AU35"/>
     <mergeCell ref="J49:P49"/>
+    <mergeCell ref="J74:P74"/>
     <mergeCell ref="AE68:AF68"/>
+    <mergeCell ref="AE74:AF74"/>
     <mergeCell ref="J36:P36"/>
     <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
     <mergeCell ref="AY66:BA66"/>
+    <mergeCell ref="AJ70:AL70"/>
     <mergeCell ref="AV21:AX21"/>
+    <mergeCell ref="AM77:AO77"/>
     <mergeCell ref="BK24:BQ24"/>
     <mergeCell ref="X45:AD45"/>
     <mergeCell ref="E50:I50"/>
@@ -17840,11 +19058,16 @@
     <mergeCell ref="E42:I42"/>
     <mergeCell ref="AY55:BA55"/>
     <mergeCell ref="AY68:BA68"/>
+    <mergeCell ref="BH71:BJ71"/>
+    <mergeCell ref="BE75:BG75"/>
+    <mergeCell ref="AG75:AI75"/>
     <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="E44:I44"/>
     <mergeCell ref="X46:AD46"/>
     <mergeCell ref="AE21:AF21"/>
+    <mergeCell ref="A69:BQ69"/>
+    <mergeCell ref="BH73:BJ73"/>
     <mergeCell ref="BE58:BG58"/>
     <mergeCell ref="AV24:AX24"/>
     <mergeCell ref="AJ65:AL65"/>
@@ -17853,20 +19076,26 @@
     <mergeCell ref="AS28:AU28"/>
     <mergeCell ref="AM31:AO31"/>
     <mergeCell ref="J29:P29"/>
+    <mergeCell ref="BE70:BG70"/>
+    <mergeCell ref="AY79:BA79"/>
     <mergeCell ref="AE23:AF23"/>
     <mergeCell ref="AC6:AE6"/>
+    <mergeCell ref="BH77:BJ77"/>
     <mergeCell ref="BB17:BD17"/>
     <mergeCell ref="AV49:AX49"/>
     <mergeCell ref="BB11:BD11"/>
     <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="B45:D45"/>
+    <mergeCell ref="BE78:BG78"/>
     <mergeCell ref="AM32:AO32"/>
     <mergeCell ref="AG64:AI64"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="J24:P24"/>
+    <mergeCell ref="BB75:BD75"/>
     <mergeCell ref="AG51:AI51"/>
     <mergeCell ref="Q20:W20"/>
     <mergeCell ref="B47:D47"/>
+    <mergeCell ref="E70:I70"/>
     <mergeCell ref="Q14:W14"/>
     <mergeCell ref="B59:D59"/>
     <mergeCell ref="E57:I57"/>
@@ -17876,6 +19105,8 @@
     <mergeCell ref="E32:I32"/>
     <mergeCell ref="BH66:BJ66"/>
     <mergeCell ref="AS41:AU41"/>
+    <mergeCell ref="Q78:W78"/>
+    <mergeCell ref="AV80:AX80"/>
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
@@ -17889,9 +19120,11 @@
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="AS43:AU43"/>
     <mergeCell ref="BH68:BJ68"/>
+    <mergeCell ref="AE76:AF76"/>
     <mergeCell ref="AY63:BA63"/>
     <mergeCell ref="BE25:BG25"/>
     <mergeCell ref="BK38:BQ38"/>
+    <mergeCell ref="Q80:W80"/>
     <mergeCell ref="F4:AH4"/>
     <mergeCell ref="X51:AD51"/>
     <mergeCell ref="AJ13:AL13"/>
@@ -17902,18 +19135,25 @@
     <mergeCell ref="J50:P50"/>
     <mergeCell ref="AP40:AR40"/>
     <mergeCell ref="BH67:BJ67"/>
+    <mergeCell ref="BE71:BG71"/>
+    <mergeCell ref="AJ78:AL78"/>
     <mergeCell ref="J42:P42"/>
     <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
     <mergeCell ref="AY67:BA67"/>
+    <mergeCell ref="BB72:BD72"/>
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="X36:AD36"/>
     <mergeCell ref="J52:P52"/>
+    <mergeCell ref="AE77:AF77"/>
+    <mergeCell ref="AJ80:AL80"/>
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="Q25:W25"/>
     <mergeCell ref="AV37:AX37"/>
     <mergeCell ref="BB65:BD65"/>
     <mergeCell ref="BE66:BG66"/>
+    <mergeCell ref="AJ79:AL79"/>
+    <mergeCell ref="Q71:W71"/>
     <mergeCell ref="X67:AD67"/>
     <mergeCell ref="J37:P37"/>
     <mergeCell ref="X61:AD61"/>
@@ -17926,6 +19166,7 @@
     <mergeCell ref="AG14:AI14"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="AV32:AX32"/>
+    <mergeCell ref="Q73:W73"/>
     <mergeCell ref="E45:I45"/>
     <mergeCell ref="AS29:AU29"/>
     <mergeCell ref="AM42:AO42"/>
@@ -17936,11 +19177,15 @@
     <mergeCell ref="AM29:AO29"/>
     <mergeCell ref="AM23:AO23"/>
     <mergeCell ref="AE24:AF24"/>
+    <mergeCell ref="BE80:BG80"/>
+    <mergeCell ref="J70:P70"/>
     <mergeCell ref="AS44:AU44"/>
     <mergeCell ref="AV27:AX27"/>
     <mergeCell ref="BE55:BG55"/>
     <mergeCell ref="AS31:AU31"/>
+    <mergeCell ref="AM71:AO71"/>
     <mergeCell ref="X64:AD64"/>
+    <mergeCell ref="AG72:AI72"/>
     <mergeCell ref="BH18:BJ18"/>
     <mergeCell ref="J32:P32"/>
     <mergeCell ref="J63:P63"/>
@@ -17956,9 +19201,13 @@
     <mergeCell ref="BB14:BD14"/>
     <mergeCell ref="AY24:BA24"/>
     <mergeCell ref="AJ28:AL28"/>
+    <mergeCell ref="E71:I71"/>
     <mergeCell ref="BK17:BQ17"/>
     <mergeCell ref="BK55:BQ55"/>
+    <mergeCell ref="J76:P76"/>
     <mergeCell ref="AP59:AR59"/>
+    <mergeCell ref="E79:I79"/>
+    <mergeCell ref="E73:I73"/>
     <mergeCell ref="AP46:AR46"/>
     <mergeCell ref="BK59:BQ59"/>
     <mergeCell ref="BK46:BQ46"/>
@@ -17969,6 +19218,7 @@
     <mergeCell ref="Q21:W21"/>
     <mergeCell ref="AP61:AR61"/>
     <mergeCell ref="AM16:AO16"/>
+    <mergeCell ref="BB80:BD80"/>
     <mergeCell ref="B64:D64"/>
     <mergeCell ref="AE44:AF44"/>
     <mergeCell ref="X57:AD57"/>
@@ -17983,44 +19233,63 @@
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="BE68:BG68"/>
     <mergeCell ref="AP43:AR43"/>
+    <mergeCell ref="BE74:BG74"/>
+    <mergeCell ref="AY77:BA77"/>
     <mergeCell ref="AM47:AO47"/>
     <mergeCell ref="B10:D11"/>
     <mergeCell ref="J45:P45"/>
     <mergeCell ref="Q35:W35"/>
+    <mergeCell ref="BB71:BD71"/>
     <mergeCell ref="AM46:AO46"/>
     <mergeCell ref="AG22:AI22"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="AJ23:AL23"/>
     <mergeCell ref="E66:I66"/>
+    <mergeCell ref="AV71:AX71"/>
+    <mergeCell ref="J79:P79"/>
+    <mergeCell ref="AE70:AF70"/>
+    <mergeCell ref="AY72:BA72"/>
+    <mergeCell ref="BB73:BD73"/>
+    <mergeCell ref="Q74:W74"/>
     <mergeCell ref="Q49:W49"/>
     <mergeCell ref="E68:I68"/>
     <mergeCell ref="BK43:BQ43"/>
     <mergeCell ref="AM44:AO44"/>
+    <mergeCell ref="AV73:AX73"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="AF6:AH6"/>
     <mergeCell ref="E55:I55"/>
+    <mergeCell ref="AV76:AX76"/>
     <mergeCell ref="AE32:AF32"/>
     <mergeCell ref="E67:I67"/>
     <mergeCell ref="AY14:BA14"/>
     <mergeCell ref="AJ18:AL18"/>
     <mergeCell ref="J51:P51"/>
     <mergeCell ref="F2:Q2"/>
+    <mergeCell ref="Q76:W76"/>
     <mergeCell ref="BH17:BJ17"/>
+    <mergeCell ref="AS70:AU70"/>
     <mergeCell ref="AE47:AF47"/>
     <mergeCell ref="BE21:BG21"/>
     <mergeCell ref="Q6:S6"/>
     <mergeCell ref="AJ34:AL34"/>
     <mergeCell ref="BK34:BQ34"/>
     <mergeCell ref="AY59:BA59"/>
+    <mergeCell ref="J71:P71"/>
+    <mergeCell ref="X72:AD72"/>
+    <mergeCell ref="AM73:AO73"/>
+    <mergeCell ref="AV77:AX77"/>
     <mergeCell ref="J58:P58"/>
     <mergeCell ref="AS32:AU32"/>
     <mergeCell ref="AM45:AO45"/>
     <mergeCell ref="AJ49:AL49"/>
     <mergeCell ref="AP11:AR11"/>
+    <mergeCell ref="X70:AD70"/>
     <mergeCell ref="BB22:BD22"/>
     <mergeCell ref="BE23:BG23"/>
     <mergeCell ref="AJ36:AL36"/>
     <mergeCell ref="BK36:BQ36"/>
+    <mergeCell ref="J73:P73"/>
     <mergeCell ref="AS47:AU47"/>
     <mergeCell ref="AY54:BA54"/>
     <mergeCell ref="AJ29:AL29"/>
@@ -18029,6 +19298,7 @@
     <mergeCell ref="BK61:BQ61"/>
     <mergeCell ref="AJ44:AL44"/>
     <mergeCell ref="Q54:W54"/>
+    <mergeCell ref="J77:P77"/>
     <mergeCell ref="AS65:AU65"/>
     <mergeCell ref="BE18:BG18"/>
     <mergeCell ref="AY27:BA27"/>
@@ -18039,6 +19309,7 @@
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="B62:D62"/>
     <mergeCell ref="AV66:AX66"/>
+    <mergeCell ref="B72:D72"/>
     <mergeCell ref="AS58:AU58"/>
     <mergeCell ref="AG34:AI34"/>
     <mergeCell ref="AV59:AX59"/>
@@ -18053,6 +19324,7 @@
     <mergeCell ref="BK62:BQ62"/>
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="BH37:BJ37"/>
+    <mergeCell ref="B70:D70"/>
     <mergeCell ref="AE45:AF45"/>
     <mergeCell ref="X58:AD58"/>
     <mergeCell ref="AV61:AX61"/>
@@ -18064,6 +19336,8 @@
     <mergeCell ref="AG59:AI59"/>
     <mergeCell ref="BK64:BQ64"/>
     <mergeCell ref="J66:P66"/>
+    <mergeCell ref="BE76:BG76"/>
+    <mergeCell ref="AG76:AI76"/>
     <mergeCell ref="BK51:BQ51"/>
     <mergeCell ref="AM67:AO67"/>
     <mergeCell ref="AM61:AO61"/>
@@ -18079,6 +19353,7 @@
     <mergeCell ref="Z8:AB8"/>
     <mergeCell ref="AP65:AR65"/>
     <mergeCell ref="AM20:AO20"/>
+    <mergeCell ref="BE77:BG77"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="J61:P61"/>
     <mergeCell ref="AY11:BA11"/>
@@ -18086,15 +19361,21 @@
     <mergeCell ref="AM35:AO35"/>
     <mergeCell ref="AS13:AU13"/>
     <mergeCell ref="AP17:AR17"/>
+    <mergeCell ref="AS78:AU78"/>
     <mergeCell ref="AY40:BA40"/>
     <mergeCell ref="Q42:W42"/>
     <mergeCell ref="A12:BQ12"/>
     <mergeCell ref="AY15:BA15"/>
+    <mergeCell ref="BB76:BD76"/>
     <mergeCell ref="AG23:AI23"/>
+    <mergeCell ref="E77:I77"/>
     <mergeCell ref="BH40:BJ40"/>
     <mergeCell ref="X13:AD13"/>
     <mergeCell ref="AS15:AU15"/>
+    <mergeCell ref="AP75:AR75"/>
     <mergeCell ref="BH27:BJ27"/>
+    <mergeCell ref="AS80:AU80"/>
+    <mergeCell ref="BK75:BQ75"/>
     <mergeCell ref="AS55:AU55"/>
     <mergeCell ref="BE37:BG37"/>
     <mergeCell ref="AJ50:AL50"/>
@@ -18106,12 +19387,15 @@
     <mergeCell ref="AM38:AO38"/>
     <mergeCell ref="BB28:BD28"/>
     <mergeCell ref="AG41:AI41"/>
+    <mergeCell ref="AS73:AU73"/>
+    <mergeCell ref="E72:I72"/>
     <mergeCell ref="BH35:BJ35"/>
     <mergeCell ref="AJ52:AL52"/>
     <mergeCell ref="AP14:AR14"/>
     <mergeCell ref="BK52:BQ52"/>
     <mergeCell ref="BH22:BJ22"/>
     <mergeCell ref="AG56:AI56"/>
+    <mergeCell ref="X73:AD73"/>
     <mergeCell ref="AM40:AO40"/>
     <mergeCell ref="J16:P16"/>
     <mergeCell ref="H6:J6"/>
@@ -18127,7 +19411,9 @@
     <mergeCell ref="E24:I24"/>
     <mergeCell ref="AG36:AI36"/>
     <mergeCell ref="B13:D13"/>
+    <mergeCell ref="Q70:W70"/>
     <mergeCell ref="AE66:AF66"/>
+    <mergeCell ref="B78:D78"/>
     <mergeCell ref="Q45:W45"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="BB31:BD31"/>
@@ -18163,8 +19449,10 @@
     <mergeCell ref="Q63:W63"/>
     <mergeCell ref="AJ40:AL40"/>
     <mergeCell ref="Q50:W50"/>
+    <mergeCell ref="AM72:AO72"/>
     <mergeCell ref="AJ27:AL27"/>
     <mergeCell ref="B22:D22"/>
+    <mergeCell ref="AS79:AU79"/>
     <mergeCell ref="AY41:BA41"/>
     <mergeCell ref="X15:AD15"/>
     <mergeCell ref="AV18:AX18"/>
@@ -18177,6 +19465,7 @@
     <mergeCell ref="AP20:AR20"/>
     <mergeCell ref="AS21:AU21"/>
     <mergeCell ref="AY43:BA43"/>
+    <mergeCell ref="X79:AD79"/>
     <mergeCell ref="BE32:BG32"/>
     <mergeCell ref="BE63:BG63"/>
     <mergeCell ref="BK14:BQ14"/>
@@ -18187,7 +19476,9 @@
     <mergeCell ref="BH43:BJ43"/>
     <mergeCell ref="BE47:BG47"/>
     <mergeCell ref="AP22:AR22"/>
+    <mergeCell ref="AP78:AR78"/>
     <mergeCell ref="B38:D38"/>
+    <mergeCell ref="BK78:BQ78"/>
     <mergeCell ref="J18:P18"/>
     <mergeCell ref="AE18:AF18"/>
     <mergeCell ref="BE40:BG40"/>
@@ -18204,16 +19495,20 @@
     <mergeCell ref="AJ45:AL45"/>
     <mergeCell ref="AG57:AI57"/>
     <mergeCell ref="E63:I63"/>
+    <mergeCell ref="AP80:AR80"/>
+    <mergeCell ref="BK80:BQ80"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="BB52:BD52"/>
     <mergeCell ref="AJ55:AL55"/>
     <mergeCell ref="AY34:BA34"/>
     <mergeCell ref="B33:D33"/>
+    <mergeCell ref="BB70:BD70"/>
     <mergeCell ref="BH59:BJ59"/>
     <mergeCell ref="AY25:BA25"/>
     <mergeCell ref="AS34:AU34"/>
     <mergeCell ref="BB45:BD45"/>
     <mergeCell ref="AG58:AI58"/>
+    <mergeCell ref="B79:D79"/>
     <mergeCell ref="BB32:BD32"/>
     <mergeCell ref="Q55:W55"/>
     <mergeCell ref="AY36:BA36"/>
@@ -18225,7 +19520,9 @@
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="AS42:AU42"/>
     <mergeCell ref="BH54:BJ54"/>
+    <mergeCell ref="AJ71:AL71"/>
     <mergeCell ref="AP33:AR33"/>
+    <mergeCell ref="BK71:BQ71"/>
     <mergeCell ref="BH41:BJ41"/>
     <mergeCell ref="BE45:BG45"/>
     <mergeCell ref="AJ58:AL58"/>
@@ -18234,7 +19531,9 @@
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BH56:BJ56"/>
     <mergeCell ref="X29:AD29"/>
+    <mergeCell ref="AJ73:AL73"/>
     <mergeCell ref="AP35:AR35"/>
+    <mergeCell ref="BK73:BQ73"/>
     <mergeCell ref="BH31:BJ31"/>
     <mergeCell ref="A39:BQ39"/>
     <mergeCell ref="AV42:AX42"/>
@@ -18243,11 +19542,15 @@
     <mergeCell ref="BB63:BD63"/>
     <mergeCell ref="AJ66:AL66"/>
     <mergeCell ref="BE46:BG46"/>
+    <mergeCell ref="AG70:AI70"/>
+    <mergeCell ref="AE72:AF72"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
+    <mergeCell ref="AP74:AR74"/>
     <mergeCell ref="BK20:BQ20"/>
     <mergeCell ref="AY28:BA28"/>
     <mergeCell ref="B34:D34"/>
+    <mergeCell ref="AJ77:AL77"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="AY64:BA64"/>
     <mergeCell ref="AJ68:AL68"/>
@@ -18259,10 +19562,12 @@
     <mergeCell ref="BK22:BQ22"/>
     <mergeCell ref="E13:I13"/>
     <mergeCell ref="X43:AD43"/>
+    <mergeCell ref="AG71:AI71"/>
     <mergeCell ref="Q68:W68"/>
     <mergeCell ref="E40:I40"/>
     <mergeCell ref="BK15:BQ15"/>
     <mergeCell ref="AE17:AF17"/>
+    <mergeCell ref="BE73:BG73"/>
     <mergeCell ref="E15:I15"/>
     <mergeCell ref="AV20:AX20"/>
     <mergeCell ref="AS24:AU24"/>
@@ -18278,8 +19583,10 @@
     <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="AJ21:AL21"/>
     <mergeCell ref="J27:P27"/>
+    <mergeCell ref="BB78:BD78"/>
     <mergeCell ref="AG25:AI25"/>
     <mergeCell ref="AY33:BA33"/>
+    <mergeCell ref="Q79:W79"/>
     <mergeCell ref="T5:AH5"/>
     <mergeCell ref="AM22:AO22"/>
     <mergeCell ref="AP23:AR23"/>
@@ -18288,6 +19595,8 @@
     <mergeCell ref="AJ61:AL61"/>
     <mergeCell ref="AV47:AX47"/>
     <mergeCell ref="B43:D43"/>
+    <mergeCell ref="AY75:BA75"/>
+    <mergeCell ref="BH80:BJ80"/>
     <mergeCell ref="BE51:BG51"/>
     <mergeCell ref="AY50:BA50"/>
     <mergeCell ref="BB55:BD55"/>
@@ -18296,9 +19605,11 @@
     <mergeCell ref="J22:P22"/>
     <mergeCell ref="BH62:BJ62"/>
     <mergeCell ref="AV38:AX38"/>
+    <mergeCell ref="X75:AD75"/>
     <mergeCell ref="AY52:BA52"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="BK35:BQ35"/>
+    <mergeCell ref="AS77:AU77"/>
     <mergeCell ref="AS52:AU52"/>
     <mergeCell ref="X44:AD44"/>
     <mergeCell ref="AP34:AR34"/>
@@ -18316,15 +19627,23 @@
     <mergeCell ref="AS37:AU37"/>
     <mergeCell ref="AE14:AF14"/>
     <mergeCell ref="BE67:BG67"/>
+    <mergeCell ref="AJ74:AL74"/>
+    <mergeCell ref="BK74:BQ74"/>
     <mergeCell ref="J38:P38"/>
+    <mergeCell ref="AM75:AO75"/>
+    <mergeCell ref="AG78:AI78"/>
     <mergeCell ref="K7:M7"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="Q28:W28"/>
+    <mergeCell ref="AP76:AR76"/>
     <mergeCell ref="AG15:AI15"/>
     <mergeCell ref="AJ16:AL16"/>
     <mergeCell ref="X32:AD32"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="E59:I59"/>
+    <mergeCell ref="AJ76:AL76"/>
+    <mergeCell ref="BK76:BQ76"/>
+    <mergeCell ref="AE78:AF78"/>
     <mergeCell ref="E46:I46"/>
     <mergeCell ref="J40:P40"/>
     <mergeCell ref="BE62:BG62"/>
@@ -18336,6 +19655,9 @@
     <mergeCell ref="E61:I61"/>
     <mergeCell ref="BB66:BD66"/>
     <mergeCell ref="Q67:W67"/>
+    <mergeCell ref="AG73:AI73"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="AG79:AI79"/>
     <mergeCell ref="AV35:AX35"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
@@ -18349,6 +19671,7 @@
     <mergeCell ref="J35:P35"/>
     <mergeCell ref="X65:AD65"/>
     <mergeCell ref="AM66:AO66"/>
+    <mergeCell ref="BH75:BJ75"/>
     <mergeCell ref="AE27:AF27"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="F3:Q3"/>
@@ -18369,9 +19692,11 @@
     <mergeCell ref="BH52:BJ52"/>
     <mergeCell ref="AS27:AU27"/>
     <mergeCell ref="A60:BQ60"/>
+    <mergeCell ref="BH79:BJ79"/>
     <mergeCell ref="AP31:AR31"/>
     <mergeCell ref="AE35:AF35"/>
     <mergeCell ref="BH14:BJ14"/>
+    <mergeCell ref="BB79:BD79"/>
     <mergeCell ref="BK54:BQ54"/>
     <mergeCell ref="AJ62:AL62"/>
     <mergeCell ref="AJ37:AL37"/>
@@ -18385,7 +19710,9 @@
     <mergeCell ref="B65:D65"/>
     <mergeCell ref="AJ64:AL64"/>
     <mergeCell ref="T7:V7"/>
+    <mergeCell ref="J72:P72"/>
     <mergeCell ref="J28:P28"/>
+    <mergeCell ref="AY78:BA78"/>
     <mergeCell ref="X52:AD52"/>
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="Q18:W18"/>
@@ -18399,8 +19726,10 @@
     <mergeCell ref="AP57:AR57"/>
     <mergeCell ref="AV41:AX41"/>
     <mergeCell ref="AE13:AF13"/>
+    <mergeCell ref="AY80:BA80"/>
     <mergeCell ref="AS45:AU45"/>
     <mergeCell ref="BK57:BQ57"/>
+    <mergeCell ref="X78:AD78"/>
     <mergeCell ref="AE40:AF40"/>
     <mergeCell ref="X47:AD47"/>
     <mergeCell ref="BH63:BJ63"/>
@@ -18418,27 +19747,37 @@
     <mergeCell ref="AM56:AO56"/>
     <mergeCell ref="AM62:AO62"/>
     <mergeCell ref="J54:P54"/>
+    <mergeCell ref="BB74:BD74"/>
+    <mergeCell ref="AE79:AF79"/>
     <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="J41:P41"/>
     <mergeCell ref="Q44:W44"/>
     <mergeCell ref="BB67:BD67"/>
     <mergeCell ref="AV43:AX43"/>
+    <mergeCell ref="BE72:BG72"/>
+    <mergeCell ref="AY71:BA71"/>
     <mergeCell ref="E62:I62"/>
     <mergeCell ref="J56:P56"/>
     <mergeCell ref="AY58:BA58"/>
+    <mergeCell ref="AS71:AU71"/>
     <mergeCell ref="J43:P43"/>
     <mergeCell ref="AM57:AO57"/>
     <mergeCell ref="X25:AD25"/>
     <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="AV72:AX72"/>
     <mergeCell ref="E64:I64"/>
+    <mergeCell ref="AY73:BA73"/>
+    <mergeCell ref="X71:AD71"/>
     <mergeCell ref="E51:I51"/>
     <mergeCell ref="BK31:BQ31"/>
     <mergeCell ref="AG18:AI18"/>
     <mergeCell ref="BE17:BG17"/>
     <mergeCell ref="B55:D55"/>
+    <mergeCell ref="AP70:AR70"/>
     <mergeCell ref="BB21:BD21"/>
     <mergeCell ref="N6:P6"/>
     <mergeCell ref="AM25:AO25"/>
+    <mergeCell ref="BH78:BJ78"/>
     <mergeCell ref="E65:I65"/>
     <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
@@ -18454,6 +19793,7 @@
     <mergeCell ref="BB16:BD16"/>
     <mergeCell ref="AG29:AI29"/>
     <mergeCell ref="AG10:AU10"/>
+    <mergeCell ref="B71:D71"/>
     <mergeCell ref="AG44:AI44"/>
     <mergeCell ref="AV62:AX62"/>
     <mergeCell ref="AM28:AO28"/>
@@ -18464,15 +19804,18 @@
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="AV56:AX56"/>
     <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E75:I75"/>
+    <mergeCell ref="AG77:AI77"/>
+    <mergeCell ref="X80:AD80"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE18 AE20:AE25 AE27:AE29 AE31:AE38 AE40:AE47 AE49:AE52 AE54:AE59 AE61:AE68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE18 AE20:AE25 AE27:AE29 AE31:AE38 AE40:AE47 AE49:AE52 AE54:AE59 AE61:AE68 AE70:AE80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG18 AG20:AG25 AG27:AG29 AG31:AG38 AG40:AG47 AG49:AG52 AG54:AG59 AG61:AG68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG18 AG20:AG25 AG27:AG29 AG31:AG38 AG40:AG47 AG49:AG52 AG54:AG59 AG61:AG68 AG70:AG80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV18 AV20:AV25 AV27:AV29 AV31:AV38 AV40:AV47 AV49:AV52 AV54:AV59 AV61:AV68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV18 AV20:AV25 AV27:AV29 AV31:AV38 AV40:AV47 AV49:AV52 AV54:AV59 AV61:AV68 AV70:AV80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
